--- a/_tmp_archive/v49_build_workdir_cleanup/CKI_Tables_NC.xlsx
+++ b/_tmp_archive/v49_build_workdir_cleanup/CKI_Tables_NC.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -418,103 +417,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Table 1. Classification AUC (area under the ROC curve) of five metrics on Tabula Sapiens (99 of 102 cell-type entries analyzed; 4,851 pairs).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>ROC-AUC</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cosine distance</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0.887</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Raw JS divergence</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.849</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Marker Jaccard distance</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0.801</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Spearman distance</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.690</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CKI ω</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>0.680</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -527,7 +429,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 2. Cross-organ conservation ranking by cell type (Tabula Sapiens, n=59 same-cell-type cross-organ pairs). Well-sampled cell types (n ≥ 5 cross-organ pairs) are ranked first by mean ω; sparsely sampled cell types (n &lt; 5 pairs; SD shown only where n &gt; 1) are listed below the divider, and their rankings should be interpreted as suggestive only. k_f-only controls for this ranking are reported in Supplementary Note 9.</t>
+          <t>Table 1. Cross-organ conservation ranking by cell type (Tabula Sapiens, n=59 same-cell-type cross-organ pairs). Well-sampled cell types (n ≥ 5 cross-organ pairs) are ranked first by mean ω; sparsely sampled cell types (n &lt; 5 pairs; SD shown only where n &gt; 1) are listed below the divider, and their rankings should be interpreted as suggestive only. Because the k_n anchor is not calibrated across cell types (Discussion), cross-type gaps in mean ω are descriptive rather than calibrated. k_f-only controls for this ranking are reported in Supplementary Note 9.</t>
         </is>
       </c>
     </row>
